--- a/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2025.xlsx
+++ b/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2025.xlsx
@@ -3422,53 +3422,41 @@
           <t>Rio Grande above Otowi</t>
         </is>
       </c>
-      <c r="F53" s="4">
-        <f>SUM(F20:F29)</f>
-        <v/>
-      </c>
-      <c r="G53" s="4">
-        <f>SUM(G20:G29)</f>
-        <v/>
-      </c>
-      <c r="H53" s="4">
-        <f>SUM(H20:H29)</f>
-        <v/>
-      </c>
-      <c r="I53" s="4">
-        <f>SUM(I20:I29)</f>
-        <v/>
-      </c>
-      <c r="J53" s="4">
-        <f>SUM(J20:J29)</f>
-        <v/>
-      </c>
-      <c r="K53" s="4">
-        <f>SUM(K20:K29)</f>
-        <v/>
-      </c>
-      <c r="L53" s="4">
-        <f>SUM(L20:L29)</f>
-        <v/>
-      </c>
-      <c r="M53" s="4">
-        <f>SUM(M20:M29)</f>
-        <v/>
-      </c>
-      <c r="N53" s="4">
-        <f>SUM(N20:N29)</f>
-        <v/>
-      </c>
-      <c r="O53" s="4">
-        <f>SUM(O20:O29)</f>
-        <v/>
-      </c>
-      <c r="P53" s="4">
-        <f>SUM(P20:P29)</f>
-        <v/>
-      </c>
-      <c r="Q53" s="4">
-        <f>SUM(Q20:Q29)</f>
-        <v/>
+      <c r="F53" s="4" t="n">
+        <v>0.141604</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0.141554</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0.141478</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0.141446</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>0.14137</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>0.141211</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>0.140988</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>0.141009</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>0.141269</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0.141568</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0.141721</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0.141647</v>
       </c>
     </row>
     <row r="54">
@@ -3477,53 +3465,41 @@
           <t>Rio Grande below Otowi</t>
         </is>
       </c>
-      <c r="F54" s="4">
-        <f>SUM(F30:F45)</f>
-        <v/>
-      </c>
-      <c r="G54" s="4">
-        <f>SUM(G30:G45)</f>
-        <v/>
-      </c>
-      <c r="H54" s="4">
-        <f>SUM(H30:H45)</f>
-        <v/>
-      </c>
-      <c r="I54" s="4">
-        <f>SUM(I30:I45)</f>
-        <v/>
-      </c>
-      <c r="J54" s="4">
-        <f>SUM(J30:J45)</f>
-        <v/>
-      </c>
-      <c r="K54" s="4">
-        <f>SUM(K30:K45)</f>
-        <v/>
-      </c>
-      <c r="L54" s="4">
-        <f>SUM(L30:L45)</f>
-        <v/>
-      </c>
-      <c r="M54" s="4">
-        <f>SUM(M30:M45)</f>
-        <v/>
-      </c>
-      <c r="N54" s="4">
-        <f>SUM(N30:N45)</f>
-        <v/>
-      </c>
-      <c r="O54" s="4">
-        <f>SUM(O30:O45)</f>
-        <v/>
-      </c>
-      <c r="P54" s="4">
-        <f>SUM(P30:P45)</f>
-        <v/>
-      </c>
-      <c r="Q54" s="4">
-        <f>SUM(Q30:Q45)</f>
-        <v/>
+      <c r="F54" s="4" t="n">
+        <v>1.227372</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>1.098981</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>1.241369</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>1.282439</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>1.132107</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>1.07544</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>1.090819</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>1.464095</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>1.455773</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>1.278961</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>1.132389</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>1.015053</v>
       </c>
     </row>
     <row r="55">
@@ -3604,57 +3580,44 @@
           <t>Above Otowi</t>
         </is>
       </c>
-      <c r="F56" s="6">
-        <f>F53*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G56" s="6">
-        <f>G53*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H56" s="6">
-        <f>H53*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>I53*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>J53*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>K53*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>L53*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>M53*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
-        <f>N53*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O56" s="6">
-        <f>O53*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P56" s="6">
-        <f>P53*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q56" s="6">
-        <f>Q53*60*60*24*Q$52/43560</f>
-        <v/>
-      </c>
-      <c r="R56" s="7">
-        <f>SUM(F56:Q56)</f>
-        <v/>
+      <c r="F56" s="6" t="n">
+        <v>8.706890578512397</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>7.861511404958678</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>8.699143140495867</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>8.416621487603305</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>8.692502479338843</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>8.402638016528925</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>8.669014214876032</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>8.670305454545455</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>8.406089256198348</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>8.704677024793389</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>8.43298512396694</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>8.709534545454545</v>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v>102.3719127272727</v>
       </c>
     </row>
     <row r="57">
@@ -3668,57 +3631,44 @@
           <t>Below Otowi</t>
         </is>
       </c>
-      <c r="F57" s="6">
-        <f>F54*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G57" s="6">
-        <f>G54*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H57" s="6">
-        <f>H54*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I57" s="6">
-        <f>I54*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J57" s="6">
-        <f>J54*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K57" s="6">
-        <f>K54*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L57" s="6">
-        <f>L54*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M57" s="6">
-        <f>M54*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N57" s="6">
-        <f>N54*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O57" s="6">
-        <f>O54*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P57" s="6">
-        <f>P54*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q57" s="6">
-        <f>Q54*60*60*24*Q$52/43560</f>
-        <v/>
-      </c>
-      <c r="R57" s="7">
-        <f>SUM(F57:Q57)</f>
-        <v/>
+      <c r="F57" s="6" t="n">
+        <v>75.46816264462812</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>61.03431669421489</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>76.32880462809916</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>76.31041983471076</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>69.61054611570249</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>63.99312396694217</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>67.07184595041322</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>90.02369256198349</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>86.62450909090907</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>78.64024661157021</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>67.38182479338843</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>62.4131761983471</v>
+      </c>
+      <c r="R57" s="7" t="n">
+        <v>874.9006690909091</v>
       </c>
     </row>
     <row r="58">
@@ -3727,53 +3677,41 @@
           <t>Total RG (sum)</t>
         </is>
       </c>
-      <c r="F58" s="6">
-        <f>SUM(F56:F57)</f>
-        <v/>
-      </c>
-      <c r="G58" s="6">
-        <f>SUM(G56:G57)</f>
-        <v/>
-      </c>
-      <c r="H58" s="6">
-        <f>SUM(H56:H57)</f>
-        <v/>
-      </c>
-      <c r="I58" s="6">
-        <f>SUM(I56:I57)</f>
-        <v/>
-      </c>
-      <c r="J58" s="6">
-        <f>SUM(J56:J57)</f>
-        <v/>
-      </c>
-      <c r="K58" s="6">
-        <f>SUM(K56:K57)</f>
-        <v/>
-      </c>
-      <c r="L58" s="6">
-        <f>SUM(L56:L57)</f>
-        <v/>
-      </c>
-      <c r="M58" s="6">
-        <f>SUM(M56:M57)</f>
-        <v/>
-      </c>
-      <c r="N58" s="6">
-        <f>SUM(N56:N57)</f>
-        <v/>
-      </c>
-      <c r="O58" s="6">
-        <f>SUM(O56:O57)</f>
-        <v/>
-      </c>
-      <c r="P58" s="6">
-        <f>SUM(P56:P57)</f>
-        <v/>
-      </c>
-      <c r="Q58" s="6">
-        <f>SUM(Q56:Q57)</f>
-        <v/>
+      <c r="F58" s="6" t="n">
+        <v>84.17505322314052</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>68.89582809917357</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>85.02794776859503</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>84.72704132231407</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>78.30304859504133</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>72.39576198347109</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>75.74086016528925</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>98.69399801652895</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>95.03059834710741</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>87.34492363636359</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>75.81480991735538</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>71.12271074380165</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -3787,53 +3725,41 @@
           <t>Total RG reported</t>
         </is>
       </c>
-      <c r="F59" s="6">
-        <f>F46*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G59" s="6">
-        <f>G46*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H59" s="6">
-        <f>H46*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I59" s="6">
-        <f>I46*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J59" s="6">
-        <f>J46*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K59" s="6">
-        <f>K46*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L59" s="6">
-        <f>L46*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M59" s="6">
-        <f>M46*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N59" s="6">
-        <f>N46*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O59" s="6">
-        <f>O46*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P59" s="6">
-        <f>P46*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q59" s="6">
-        <f>Q46*60*60*24*Q$52/43560</f>
-        <v/>
+      <c r="F59" s="6" t="n">
+        <v>84.17499173553719</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>68.89582809917356</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>85.02794776859504</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>84.72704132231407</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>78.30317157024793</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>72.39576198347108</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>75.74086016528928</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>98.69399801652894</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>95.03059834710744</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>87.34498512396695</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v>75.81463140495867</v>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v>71.12258776859505</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -3849,57 +3775,44 @@
 Buckman 1, 7, 8; Row 13, Column 11</t>
         </is>
       </c>
-      <c r="F60" s="6">
-        <f>F32*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G60" s="6">
-        <f>G32*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H60" s="6">
-        <f>H32*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I60" s="6">
-        <f>I32*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J60" s="6">
-        <f>J32*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K60" s="6">
-        <f>K32*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L60" s="6">
-        <f>L32*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M60" s="6">
-        <f>M32*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N60" s="6">
-        <f>N32*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O60" s="6">
-        <f>O32*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P60" s="6">
-        <f>P32*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q60" s="6">
-        <f>Q32*60*60*24*Q$52/43560</f>
-        <v/>
-      </c>
-      <c r="R60" s="7">
-        <f>SUM(F60:Q60)</f>
-        <v/>
+      <c r="F60" s="6" t="n">
+        <v>42.92080661157025</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>31.89384198347108</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>44.08372165289256</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>45.00779504132232</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>37.43328396694214</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>33.10500495867768</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>35.35285090909091</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>57.67850776859503</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>54.81276694214876</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>45.67336066115702</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v>35.7087867768595</v>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v>30.13009388429752</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>493.8008211570248</v>
       </c>
     </row>
   </sheetData>

--- a/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2025.xlsx
+++ b/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2025.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,18 @@
     <font>
       <name val="Aptos"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -74,6 +86,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3815,6 +3830,461 @@
         <v>493.8008211570248</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK (formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUMIF: above Otowi</t>
+        </is>
+      </c>
+      <c r="F63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",F$2:F$45)-F53</f>
+        <v/>
+      </c>
+      <c r="G63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",G$2:G$45)-G53</f>
+        <v/>
+      </c>
+      <c r="H63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",H$2:H$45)-H53</f>
+        <v/>
+      </c>
+      <c r="I63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",I$2:I$45)-I53</f>
+        <v/>
+      </c>
+      <c r="J63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",J$2:J$45)-J53</f>
+        <v/>
+      </c>
+      <c r="K63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",K$2:K$45)-K53</f>
+        <v/>
+      </c>
+      <c r="L63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",L$2:L$45)-L53</f>
+        <v/>
+      </c>
+      <c r="M63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",M$2:M$45)-M53</f>
+        <v/>
+      </c>
+      <c r="N63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",N$2:N$45)-N53</f>
+        <v/>
+      </c>
+      <c r="O63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",O$2:O$45)-O53</f>
+        <v/>
+      </c>
+      <c r="P63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",P$2:P$45)-P53</f>
+        <v/>
+      </c>
+      <c r="Q63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",Q$2:Q$45)-Q53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUMIF: below Otowi</t>
+        </is>
+      </c>
+      <c r="F64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",F$2:F$45)-F54</f>
+        <v/>
+      </c>
+      <c r="G64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",G$2:G$45)-G54</f>
+        <v/>
+      </c>
+      <c r="H64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",H$2:H$45)-H54</f>
+        <v/>
+      </c>
+      <c r="I64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",I$2:I$45)-I54</f>
+        <v/>
+      </c>
+      <c r="J64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",J$2:J$45)-J54</f>
+        <v/>
+      </c>
+      <c r="K64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",K$2:K$45)-K54</f>
+        <v/>
+      </c>
+      <c r="L64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",L$2:L$45)-L54</f>
+        <v/>
+      </c>
+      <c r="M64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",M$2:M$45)-M54</f>
+        <v/>
+      </c>
+      <c r="N64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",N$2:N$45)-N54</f>
+        <v/>
+      </c>
+      <c r="O64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",O$2:O$45)-O54</f>
+        <v/>
+      </c>
+      <c r="P64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",P$2:P$45)-P54</f>
+        <v/>
+      </c>
+      <c r="Q64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",Q$2:Q$45)-Q54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUM: above (rows 20-29)</t>
+        </is>
+      </c>
+      <c r="F65" s="11">
+        <f>SUM(F20:F29)-F53</f>
+        <v/>
+      </c>
+      <c r="G65" s="11">
+        <f>SUM(G20:G29)-G53</f>
+        <v/>
+      </c>
+      <c r="H65" s="11">
+        <f>SUM(H20:H29)-H53</f>
+        <v/>
+      </c>
+      <c r="I65" s="11">
+        <f>SUM(I20:I29)-I53</f>
+        <v/>
+      </c>
+      <c r="J65" s="11">
+        <f>SUM(J20:J29)-J53</f>
+        <v/>
+      </c>
+      <c r="K65" s="11">
+        <f>SUM(K20:K29)-K53</f>
+        <v/>
+      </c>
+      <c r="L65" s="11">
+        <f>SUM(L20:L29)-L53</f>
+        <v/>
+      </c>
+      <c r="M65" s="11">
+        <f>SUM(M20:M29)-M53</f>
+        <v/>
+      </c>
+      <c r="N65" s="11">
+        <f>SUM(N20:N29)-N53</f>
+        <v/>
+      </c>
+      <c r="O65" s="11">
+        <f>SUM(O20:O29)-O53</f>
+        <v/>
+      </c>
+      <c r="P65" s="11">
+        <f>SUM(P20:P29)-P53</f>
+        <v/>
+      </c>
+      <c r="Q65" s="11">
+        <f>SUM(Q20:Q29)-Q53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUM: below (rows 30-45)</t>
+        </is>
+      </c>
+      <c r="F66" s="11">
+        <f>SUM(F30:F45)-F54</f>
+        <v/>
+      </c>
+      <c r="G66" s="11">
+        <f>SUM(G30:G45)-G54</f>
+        <v/>
+      </c>
+      <c r="H66" s="11">
+        <f>SUM(H30:H45)-H54</f>
+        <v/>
+      </c>
+      <c r="I66" s="11">
+        <f>SUM(I30:I45)-I54</f>
+        <v/>
+      </c>
+      <c r="J66" s="11">
+        <f>SUM(J30:J45)-J54</f>
+        <v/>
+      </c>
+      <c r="K66" s="11">
+        <f>SUM(K30:K45)-K54</f>
+        <v/>
+      </c>
+      <c r="L66" s="11">
+        <f>SUM(L30:L45)-L54</f>
+        <v/>
+      </c>
+      <c r="M66" s="11">
+        <f>SUM(M30:M45)-M54</f>
+        <v/>
+      </c>
+      <c r="N66" s="11">
+        <f>SUM(N30:N45)-N54</f>
+        <v/>
+      </c>
+      <c r="O66" s="11">
+        <f>SUM(O30:O45)-O54</f>
+        <v/>
+      </c>
+      <c r="P66" s="11">
+        <f>SUM(P30:P45)-P54</f>
+        <v/>
+      </c>
+      <c r="Q66" s="11">
+        <f>SUM(Q30:Q45)-Q54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>AF check: above Otowi</t>
+        </is>
+      </c>
+      <c r="F67" s="11">
+        <f>F53*F52*86400/43560-F56</f>
+        <v/>
+      </c>
+      <c r="G67" s="11">
+        <f>G53*G52*86400/43560-G56</f>
+        <v/>
+      </c>
+      <c r="H67" s="11">
+        <f>H53*H52*86400/43560-H56</f>
+        <v/>
+      </c>
+      <c r="I67" s="11">
+        <f>I53*I52*86400/43560-I56</f>
+        <v/>
+      </c>
+      <c r="J67" s="11">
+        <f>J53*J52*86400/43560-J56</f>
+        <v/>
+      </c>
+      <c r="K67" s="11">
+        <f>K53*K52*86400/43560-K56</f>
+        <v/>
+      </c>
+      <c r="L67" s="11">
+        <f>L53*L52*86400/43560-L56</f>
+        <v/>
+      </c>
+      <c r="M67" s="11">
+        <f>M53*M52*86400/43560-M56</f>
+        <v/>
+      </c>
+      <c r="N67" s="11">
+        <f>N53*N52*86400/43560-N56</f>
+        <v/>
+      </c>
+      <c r="O67" s="11">
+        <f>O53*O52*86400/43560-O56</f>
+        <v/>
+      </c>
+      <c r="P67" s="11">
+        <f>P53*P52*86400/43560-P56</f>
+        <v/>
+      </c>
+      <c r="Q67" s="11">
+        <f>Q53*Q52*86400/43560-Q56</f>
+        <v/>
+      </c>
+      <c r="R67" s="11">
+        <f>SUM(F67:Q67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>AF check: below Otowi</t>
+        </is>
+      </c>
+      <c r="F68" s="11">
+        <f>F54*F52*86400/43560-F57</f>
+        <v/>
+      </c>
+      <c r="G68" s="11">
+        <f>G54*G52*86400/43560-G57</f>
+        <v/>
+      </c>
+      <c r="H68" s="11">
+        <f>H54*H52*86400/43560-H57</f>
+        <v/>
+      </c>
+      <c r="I68" s="11">
+        <f>I54*I52*86400/43560-I57</f>
+        <v/>
+      </c>
+      <c r="J68" s="11">
+        <f>J54*J52*86400/43560-J57</f>
+        <v/>
+      </c>
+      <c r="K68" s="11">
+        <f>K54*K52*86400/43560-K57</f>
+        <v/>
+      </c>
+      <c r="L68" s="11">
+        <f>L54*L52*86400/43560-L57</f>
+        <v/>
+      </c>
+      <c r="M68" s="11">
+        <f>M54*M52*86400/43560-M57</f>
+        <v/>
+      </c>
+      <c r="N68" s="11">
+        <f>N54*N52*86400/43560-N57</f>
+        <v/>
+      </c>
+      <c r="O68" s="11">
+        <f>O54*O52*86400/43560-O57</f>
+        <v/>
+      </c>
+      <c r="P68" s="11">
+        <f>P54*P52*86400/43560-P57</f>
+        <v/>
+      </c>
+      <c r="Q68" s="11">
+        <f>Q54*Q52*86400/43560-Q57</f>
+        <v/>
+      </c>
+      <c r="R68" s="11">
+        <f>SUM(F68:Q68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Total check: above+below−sum</t>
+        </is>
+      </c>
+      <c r="F69" s="11">
+        <f>F56+F57-F58</f>
+        <v/>
+      </c>
+      <c r="G69" s="11">
+        <f>G56+G57-G58</f>
+        <v/>
+      </c>
+      <c r="H69" s="11">
+        <f>H56+H57-H58</f>
+        <v/>
+      </c>
+      <c r="I69" s="11">
+        <f>I56+I57-I58</f>
+        <v/>
+      </c>
+      <c r="J69" s="11">
+        <f>J56+J57-J58</f>
+        <v/>
+      </c>
+      <c r="K69" s="11">
+        <f>K56+K57-K58</f>
+        <v/>
+      </c>
+      <c r="L69" s="11">
+        <f>L56+L57-L58</f>
+        <v/>
+      </c>
+      <c r="M69" s="11">
+        <f>M56+M57-M58</f>
+        <v/>
+      </c>
+      <c r="N69" s="11">
+        <f>N56+N57-N58</f>
+        <v/>
+      </c>
+      <c r="O69" s="11">
+        <f>O56+O57-O58</f>
+        <v/>
+      </c>
+      <c r="P69" s="11">
+        <f>P56+P57-P58</f>
+        <v/>
+      </c>
+      <c r="Q69" s="11">
+        <f>Q56+Q57-Q58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>RG reported check: sum−sfmodflx</t>
+        </is>
+      </c>
+      <c r="F70" s="11">
+        <f>F58-F59</f>
+        <v/>
+      </c>
+      <c r="G70" s="11">
+        <f>G58-G59</f>
+        <v/>
+      </c>
+      <c r="H70" s="11">
+        <f>H58-H59</f>
+        <v/>
+      </c>
+      <c r="I70" s="11">
+        <f>I58-I59</f>
+        <v/>
+      </c>
+      <c r="J70" s="11">
+        <f>J58-J59</f>
+        <v/>
+      </c>
+      <c r="K70" s="11">
+        <f>K58-K59</f>
+        <v/>
+      </c>
+      <c r="L70" s="11">
+        <f>L58-L59</f>
+        <v/>
+      </c>
+      <c r="M70" s="11">
+        <f>M58-M59</f>
+        <v/>
+      </c>
+      <c r="N70" s="11">
+        <f>N58-N59</f>
+        <v/>
+      </c>
+      <c r="O70" s="11">
+        <f>O58-O59</f>
+        <v/>
+      </c>
+      <c r="P70" s="11">
+        <f>P58-P59</f>
+        <v/>
+      </c>
+      <c r="Q70" s="11">
+        <f>Q58-Q59</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
